--- a/Daily_Report/Top 7 broker List with its Turnover 2022-12-26.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2022-12-26.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="264">
   <si>
     <t>Date: 2022-12-26</t>
   </si>
@@ -62,12 +62,12 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
@@ -83,12 +83,12 @@
     <t>58</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
@@ -101,67 +101,67 @@
     <t>57</t>
   </si>
   <si>
-    <t>368,309,065.87</t>
-  </si>
-  <si>
-    <t>208,216,345.2</t>
-  </si>
-  <si>
-    <t>203,998,346.8</t>
-  </si>
-  <si>
-    <t>189,333,201.5</t>
-  </si>
-  <si>
-    <t>180,156,285.39</t>
-  </si>
-  <si>
-    <t>144,604,698.19</t>
-  </si>
-  <si>
-    <t>137,082,921.6</t>
-  </si>
-  <si>
-    <t>174,411,584.18</t>
-  </si>
-  <si>
-    <t>103,143,667.2</t>
-  </si>
-  <si>
-    <t>101,553,192.7</t>
-  </si>
-  <si>
-    <t>103,079,931.2</t>
-  </si>
-  <si>
-    <t>92,484,617.1</t>
-  </si>
-  <si>
-    <t>67,849,167.7</t>
-  </si>
-  <si>
-    <t>71,960,928.2</t>
-  </si>
-  <si>
-    <t>193,897,481.69</t>
-  </si>
-  <si>
-    <t>105,072,678.0</t>
-  </si>
-  <si>
-    <t>102,445,154.1</t>
-  </si>
-  <si>
-    <t>86,253,270.3</t>
-  </si>
-  <si>
-    <t>87,671,668.3</t>
-  </si>
-  <si>
-    <t>76,755,530.5</t>
-  </si>
-  <si>
-    <t>65,121,993.4</t>
+    <t>388,678,208.87</t>
+  </si>
+  <si>
+    <t>205,246,395.7</t>
+  </si>
+  <si>
+    <t>203,743,296.4</t>
+  </si>
+  <si>
+    <t>199,899,666.0</t>
+  </si>
+  <si>
+    <t>177,175,870.3</t>
+  </si>
+  <si>
+    <t>157,096,436.6</t>
+  </si>
+  <si>
+    <t>133,260,070.9</t>
+  </si>
+  <si>
+    <t>170,071,828.88</t>
+  </si>
+  <si>
+    <t>104,765,849.2</t>
+  </si>
+  <si>
+    <t>106,775,871.7</t>
+  </si>
+  <si>
+    <t>96,276,034.8</t>
+  </si>
+  <si>
+    <t>88,770,063.3</t>
+  </si>
+  <si>
+    <t>77,391,172.2</t>
+  </si>
+  <si>
+    <t>72,804,290.2</t>
+  </si>
+  <si>
+    <t>218,606,379.99</t>
+  </si>
+  <si>
+    <t>100,480,546.5</t>
+  </si>
+  <si>
+    <t>96,967,424.7</t>
+  </si>
+  <si>
+    <t>103,623,631.2</t>
+  </si>
+  <si>
+    <t>88,405,807.0</t>
+  </si>
+  <si>
+    <t>79,705,264.4</t>
+  </si>
+  <si>
+    <t>60,455,780.7</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,31 +182,58 @@
     <t>RIDI</t>
   </si>
   <si>
-    <t>23,934,846.4</t>
+    <t>22,445,066.4</t>
   </si>
   <si>
     <t>NABIL</t>
   </si>
   <si>
-    <t>14,407,054.6</t>
+    <t>16,464,642.6</t>
   </si>
   <si>
     <t>HDL</t>
   </si>
   <si>
-    <t>11,436,614.5</t>
+    <t>11,669,864.5</t>
   </si>
   <si>
     <t>NICA</t>
   </si>
   <si>
-    <t>9,959,793.6</t>
+    <t>10,261,311.1</t>
   </si>
   <si>
     <t>CBL</t>
   </si>
   <si>
-    <t>9,001,148.4</t>
+    <t>9,004,673.19</t>
+  </si>
+  <si>
+    <t>7,721,105.5</t>
+  </si>
+  <si>
+    <t>NTC</t>
+  </si>
+  <si>
+    <t>6,616,535.5</t>
+  </si>
+  <si>
+    <t>NBL</t>
+  </si>
+  <si>
+    <t>4,888,790.8</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>4,254,089.09</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>3,668,910.0</t>
   </si>
   <si>
     <t>LICN</t>
@@ -215,76 +242,46 @@
     <t>10,234,755.0</t>
   </si>
   <si>
+    <t>8,263,741.0</t>
+  </si>
+  <si>
+    <t>ALICL</t>
+  </si>
+  <si>
+    <t>8,144,686.0</t>
+  </si>
+  <si>
     <t>API</t>
   </si>
   <si>
-    <t>9,256,595.69</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>8,144,686.0</t>
-  </si>
-  <si>
-    <t>MLBL</t>
-  </si>
-  <si>
-    <t>7,196,534.4</t>
-  </si>
-  <si>
-    <t>7,134,081.0</t>
-  </si>
-  <si>
-    <t>6,827,245.5</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>5,375,508.0</t>
-  </si>
-  <si>
-    <t>NBL</t>
-  </si>
-  <si>
-    <t>4,888,790.8</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>4,254,089.09</t>
-  </si>
-  <si>
-    <t>SRBL</t>
-  </si>
-  <si>
-    <t>3,789,190.9</t>
-  </si>
-  <si>
-    <t>15,841,087.5</t>
+    <t>7,937,195.7</t>
+  </si>
+  <si>
+    <t>7,046,134.0</t>
+  </si>
+  <si>
+    <t>12,806,389.5</t>
   </si>
   <si>
     <t>7,279,093.1</t>
   </si>
   <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>5,684,264.0</t>
-  </si>
-  <si>
-    <t>4,539,336.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>4,337,938.4</t>
-  </si>
-  <si>
-    <t>27,728,887.0</t>
+    <t>5,040,566.0</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>4,735,310.4</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>4,551,978.59</t>
+  </si>
+  <si>
+    <t>30,818,355.0</t>
   </si>
   <si>
     <t>NIB</t>
@@ -293,193 +290,190 @@
     <t>9,377,956.0</t>
   </si>
   <si>
-    <t>5,727,880.0</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>4,449,836.5</t>
-  </si>
-  <si>
-    <t>3,535,630.4</t>
-  </si>
-  <si>
-    <t>12,490,430.0</t>
-  </si>
-  <si>
-    <t>3,818,646.8</t>
-  </si>
-  <si>
-    <t>GRDBL</t>
-  </si>
-  <si>
-    <t>2,768,436.0</t>
+    <t>3,864,138.4</t>
+  </si>
+  <si>
+    <t>2,940,546.0</t>
+  </si>
+  <si>
+    <t>2,592,286.5</t>
+  </si>
+  <si>
+    <t>18,235,634.0</t>
   </si>
   <si>
     <t>EBL</t>
   </si>
   <si>
-    <t>2,494,504.0</t>
-  </si>
-  <si>
-    <t>1,897,184.6</t>
-  </si>
-  <si>
-    <t>5,455,915.7</t>
+    <t>3,353,876.0</t>
+  </si>
+  <si>
+    <t>EDBL</t>
+  </si>
+  <si>
+    <t>2,927,128.0</t>
+  </si>
+  <si>
+    <t>2,556,501.0</t>
+  </si>
+  <si>
+    <t>KSBBL</t>
+  </si>
+  <si>
+    <t>2,093,395.7</t>
+  </si>
+  <si>
+    <t>5,636,915.7</t>
+  </si>
+  <si>
+    <t>4,250,695.0</t>
+  </si>
+  <si>
+    <t>3,708,103.0</t>
+  </si>
+  <si>
+    <t>AKBSL</t>
+  </si>
+  <si>
+    <t>3,573,975.7</t>
+  </si>
+  <si>
+    <t>2,684,168.6</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>122,487,693.7</t>
+  </si>
+  <si>
+    <t>8,330,985.2</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>6,577,536.2</t>
+  </si>
+  <si>
+    <t>CYCL</t>
+  </si>
+  <si>
+    <t>4,076,982.7</t>
+  </si>
+  <si>
+    <t>2,876,790.0</t>
+  </si>
+  <si>
+    <t>14,727,633.1</t>
+  </si>
+  <si>
+    <t>4,732,804.09</t>
+  </si>
+  <si>
+    <t>CCBL</t>
+  </si>
+  <si>
+    <t>4,089,840.7</t>
+  </si>
+  <si>
+    <t>CBBL</t>
+  </si>
+  <si>
+    <t>4,066,151.7</t>
+  </si>
+  <si>
+    <t>3,588,182.9</t>
+  </si>
+  <si>
+    <t>11,517,351.4</t>
+  </si>
+  <si>
+    <t>9,183,859.0</t>
+  </si>
+  <si>
+    <t>7,284,067.6</t>
+  </si>
+  <si>
+    <t>6,515,007.5</t>
+  </si>
+  <si>
+    <t>6,314,575.0</t>
+  </si>
+  <si>
+    <t>28,157,497.4</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>9,079,753.0</t>
+  </si>
+  <si>
+    <t>6,128,441.8</t>
+  </si>
+  <si>
+    <t>3,251,663.0</t>
+  </si>
+  <si>
+    <t>2,486,745.29</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>14,139,087.0</t>
+  </si>
+  <si>
+    <t>12,224,602.4</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>9,064,929.3</t>
+  </si>
+  <si>
+    <t>4,497,847.59</t>
+  </si>
+  <si>
+    <t>3,605,555.5</t>
+  </si>
+  <si>
+    <t>6,740,700.0</t>
+  </si>
+  <si>
+    <t>4,987,150.0</t>
+  </si>
+  <si>
+    <t>4,906,225.7</t>
+  </si>
+  <si>
+    <t>4,888,856.0</t>
+  </si>
+  <si>
+    <t>PCBL</t>
+  </si>
+  <si>
+    <t>4,245,124.9</t>
+  </si>
+  <si>
+    <t>6,241,892.0</t>
   </si>
   <si>
     <t>JALPA</t>
   </si>
   <si>
-    <t>4,440,745.0</t>
-  </si>
-  <si>
-    <t>3,743,224.0</t>
-  </si>
-  <si>
-    <t>AKBSL</t>
-  </si>
-  <si>
-    <t>3,384,669.7</t>
-  </si>
-  <si>
-    <t>2,885,858.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>106,412,960.7</t>
-  </si>
-  <si>
-    <t>6,488,969.7</t>
-  </si>
-  <si>
-    <t>GHL</t>
-  </si>
-  <si>
-    <t>3,921,594.2</t>
-  </si>
-  <si>
-    <t>3,596,902.5</t>
-  </si>
-  <si>
-    <t>3,265,430.0</t>
-  </si>
-  <si>
-    <t>16,346,527.4</t>
-  </si>
-  <si>
-    <t>9,183,859.0</t>
-  </si>
-  <si>
-    <t>MMFDB</t>
-  </si>
-  <si>
-    <t>7,270,749.5</t>
-  </si>
-  <si>
-    <t>7,051,104.4</t>
-  </si>
-  <si>
-    <t>6,314,575.0</t>
-  </si>
-  <si>
-    <t>CCBL</t>
-  </si>
-  <si>
-    <t>13,292,000.7</t>
-  </si>
-  <si>
-    <t>9,268,998.19</t>
-  </si>
-  <si>
-    <t>5,615,588.0</t>
-  </si>
-  <si>
-    <t>4,556,346.0</t>
-  </si>
-  <si>
-    <t>3,547,232.9</t>
-  </si>
-  <si>
-    <t>19,170,419.39</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>8,935,553.0</t>
-  </si>
-  <si>
-    <t>5,220,750.8</t>
-  </si>
-  <si>
-    <t>2,746,449.0</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>1,728,795.0</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>13,264,463.0</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>12,746,376.8</t>
-  </si>
-  <si>
-    <t>11,310,574.9</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>6,452,895.0</t>
-  </si>
-  <si>
-    <t>3,603,797.6</t>
-  </si>
-  <si>
-    <t>6,701,800.0</t>
-  </si>
-  <si>
-    <t>4,906,225.7</t>
-  </si>
-  <si>
-    <t>4,888,856.0</t>
-  </si>
-  <si>
-    <t>4,268,106.0</t>
-  </si>
-  <si>
-    <t>4,120,070.0</t>
-  </si>
-  <si>
-    <t>10,332,723.5</t>
-  </si>
-  <si>
-    <t>6,207,892.0</t>
-  </si>
-  <si>
-    <t>3,366,297.0</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>2,450,937.29</t>
-  </si>
-  <si>
-    <t>2,436,409.2</t>
+    <t>5,341,519.5</t>
+  </si>
+  <si>
+    <t>4,011,194.5</t>
+  </si>
+  <si>
+    <t>2,505,809.2</t>
+  </si>
+  <si>
+    <t>2,017,895.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -497,103 +491,103 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>188,410,234.4</t>
-  </si>
-  <si>
-    <t>101,917,077.6</t>
-  </si>
-  <si>
-    <t>77,607,709.5</t>
-  </si>
-  <si>
-    <t>71,733,851.8</t>
-  </si>
-  <si>
-    <t>60,472,764.3</t>
+    <t>208,807,244.9</t>
+  </si>
+  <si>
+    <t>111,147,077.6</t>
+  </si>
+  <si>
+    <t>91,121,150.2</t>
+  </si>
+  <si>
+    <t>72,617,407.59</t>
+  </si>
+  <si>
+    <t>68,723,509.4</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>494,476,974.7</t>
+    <t>498,798,364.5</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>389,501,221.7</t>
+    <t>398,039,062.1</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>263,517,889.5</t>
+    <t>263,731,268.06</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>219,815,526.3</t>
+    <t>243,574,147.4</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>185,803,744.3</t>
+    <t>174,083,935.8</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>146,873,778.4</t>
+    <t>159,693,453.4</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>96,609,855.0</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>97,151,471.6</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>90,950,418.6</t>
+    <t>94,801,658.0</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>66,425,126.7</t>
+    <t>69,913,755.7</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>60,552,959.1</t>
+    <t>63,603,773.4</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>22,564,165.7</t>
+    <t>24,162,317.2</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>4,771,984.2</t>
+    <t>4,988,669.2</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>3,170,665.34</t>
+    <t>2,951,112.59</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>2,026,809.0</t>
+    <t>2,098,569.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -605,214 +599,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>51,140,775.1</t>
-  </si>
-  <si>
-    <t>43,202,814.6</t>
-  </si>
-  <si>
-    <t>18,740,601.8</t>
-  </si>
-  <si>
-    <t>14,886,910.5</t>
-  </si>
-  <si>
-    <t>11,680,489.6</t>
-  </si>
-  <si>
-    <t>25,663,710.9</t>
-  </si>
-  <si>
-    <t>18,740,921.0</t>
-  </si>
-  <si>
-    <t>15,654,433.6</t>
-  </si>
-  <si>
-    <t>11,170,370.0</t>
-  </si>
-  <si>
-    <t>9,708,588.4</t>
-  </si>
-  <si>
-    <t>23,862,069.9</t>
-  </si>
-  <si>
-    <t>22,023,015.8</t>
-  </si>
-  <si>
-    <t>16,155,299.6</t>
-  </si>
-  <si>
-    <t>10,973,074.2</t>
-  </si>
-  <si>
-    <t>6,970,398.0</t>
-  </si>
-  <si>
-    <t>30,966,084.0</t>
-  </si>
-  <si>
-    <t>17,032,498.0</t>
-  </si>
-  <si>
-    <t>16,507,866.2</t>
-  </si>
-  <si>
-    <t>8,972,516.19</t>
-  </si>
-  <si>
-    <t>7,340,437.3</t>
-  </si>
-  <si>
-    <t>29,575,929.0</t>
-  </si>
-  <si>
-    <t>17,062,237.0</t>
-  </si>
-  <si>
-    <t>13,338,841.6</t>
-  </si>
-  <si>
-    <t>11,583,431.7</t>
-  </si>
-  <si>
-    <t>7,912,023.0</t>
-  </si>
-  <si>
-    <t>14,276,809.9</t>
-  </si>
-  <si>
-    <t>14,207,280.0</t>
-  </si>
-  <si>
-    <t>11,050,923.8</t>
-  </si>
-  <si>
-    <t>9,685,818.9</t>
-  </si>
-  <si>
-    <t>7,904,775.2</t>
-  </si>
-  <si>
-    <t>17,342,478.0</t>
-  </si>
-  <si>
-    <t>14,769,138.1</t>
-  </si>
-  <si>
-    <t>12,007,917.7</t>
-  </si>
-  <si>
-    <t>5,427,241.0</t>
-  </si>
-  <si>
-    <t>5,371,294.7</t>
-  </si>
-  <si>
-    <t>108,646,310.7</t>
-  </si>
-  <si>
-    <t>27,769,304.0</t>
-  </si>
-  <si>
-    <t>14,793,749.2</t>
-  </si>
-  <si>
-    <t>14,735,417.3</t>
-  </si>
-  <si>
-    <t>7,292,542.8</t>
-  </si>
-  <si>
-    <t>29,904,781.3</t>
-  </si>
-  <si>
-    <t>18,496,131.3</t>
-  </si>
-  <si>
-    <t>16,192,823.0</t>
-  </si>
-  <si>
-    <t>15,589,117.6</t>
-  </si>
-  <si>
-    <t>13,953,439.0</t>
-  </si>
-  <si>
-    <t>29,440,130.8</t>
-  </si>
-  <si>
-    <t>25,990,232.8</t>
-  </si>
-  <si>
-    <t>10,659,115.5</t>
-  </si>
-  <si>
-    <t>8,806,758.9</t>
-  </si>
-  <si>
-    <t>5,666,480.0</t>
-  </si>
-  <si>
-    <t>19,736,175.39</t>
-  </si>
-  <si>
-    <t>19,662,394.6</t>
-  </si>
-  <si>
-    <t>11,572,343.8</t>
-  </si>
-  <si>
-    <t>9,895,331.1</t>
-  </si>
-  <si>
-    <t>9,248,100.0</t>
-  </si>
-  <si>
-    <t>33,297,639.6</t>
-  </si>
-  <si>
-    <t>19,225,752.7</t>
-  </si>
-  <si>
-    <t>13,277,783.0</t>
-  </si>
-  <si>
-    <t>4,436,851.7</t>
-  </si>
-  <si>
-    <t>4,233,703.3</t>
-  </si>
-  <si>
-    <t>17,656,608.0</t>
-  </si>
-  <si>
-    <t>14,851,341.9</t>
-  </si>
-  <si>
-    <t>13,435,142.5</t>
-  </si>
-  <si>
-    <t>7,359,504.1</t>
-  </si>
-  <si>
-    <t>5,902,844.5</t>
-  </si>
-  <si>
-    <t>17,529,564.0</t>
-  </si>
-  <si>
-    <t>11,626,179.0</t>
-  </si>
-  <si>
-    <t>10,897,708.1</t>
-  </si>
-  <si>
-    <t>10,705,613.1</t>
-  </si>
-  <si>
-    <t>4,833,618.5</t>
+    <t>50,102,544.1</t>
+  </si>
+  <si>
+    <t>46,071,849.4</t>
+  </si>
+  <si>
+    <t>16,263,975.8</t>
+  </si>
+  <si>
+    <t>13,764,300.5</t>
+  </si>
+  <si>
+    <t>10,288,795.8</t>
+  </si>
+  <si>
+    <t>24,225,896.1</t>
+  </si>
+  <si>
+    <t>20,007,229.2</t>
+  </si>
+  <si>
+    <t>17,994,648.0</t>
+  </si>
+  <si>
+    <t>11,342,662.7</t>
+  </si>
+  <si>
+    <t>8,444,665.5</t>
+  </si>
+  <si>
+    <t>25,469,182.9</t>
+  </si>
+  <si>
+    <t>18,758,495.0</t>
+  </si>
+  <si>
+    <t>16,874,748.1</t>
+  </si>
+  <si>
+    <t>11,822,655.0</t>
+  </si>
+  <si>
+    <t>9,093,553.0</t>
+  </si>
+  <si>
+    <t>26,187,121.0</t>
+  </si>
+  <si>
+    <t>13,473,168.2</t>
+  </si>
+  <si>
+    <t>12,900,645.1</t>
+  </si>
+  <si>
+    <t>9,909,876.4</t>
+  </si>
+  <si>
+    <t>9,007,046.19</t>
+  </si>
+  <si>
+    <t>32,665,397.0</t>
+  </si>
+  <si>
+    <t>17,772,790.0</t>
+  </si>
+  <si>
+    <t>11,466,457.8</t>
+  </si>
+  <si>
+    <t>8,944,236.5</t>
+  </si>
+  <si>
+    <t>5,026,346.2</t>
+  </si>
+  <si>
+    <t>19,959,294.0</t>
+  </si>
+  <si>
+    <t>13,466,005.9</t>
+  </si>
+  <si>
+    <t>12,577,812.8</t>
+  </si>
+  <si>
+    <t>11,895,298.4</t>
+  </si>
+  <si>
+    <t>7,046,874.2</t>
+  </si>
+  <si>
+    <t>16,615,826.6</t>
+  </si>
+  <si>
+    <t>13,777,160.5</t>
+  </si>
+  <si>
+    <t>11,083,727.7</t>
+  </si>
+  <si>
+    <t>6,814,174.7</t>
+  </si>
+  <si>
+    <t>5,996,144.0</t>
+  </si>
+  <si>
+    <t>124,721,043.7</t>
+  </si>
+  <si>
+    <t>28,980,898.5</t>
+  </si>
+  <si>
+    <t>18,529,126.1</t>
+  </si>
+  <si>
+    <t>16,558,724.7</t>
+  </si>
+  <si>
+    <t>7,297,064.8</t>
+  </si>
+  <si>
+    <t>20,464,768.2</t>
+  </si>
+  <si>
+    <t>19,528,217.1</t>
+  </si>
+  <si>
+    <t>14,847,025.1</t>
+  </si>
+  <si>
+    <t>14,103,145.0</t>
+  </si>
+  <si>
+    <t>9,309,162.0</t>
+  </si>
+  <si>
+    <t>26,600,255.4</t>
+  </si>
+  <si>
+    <t>16,205,636.0</t>
+  </si>
+  <si>
+    <t>13,691,349.6</t>
+  </si>
+  <si>
+    <t>13,378,993.1</t>
+  </si>
+  <si>
+    <t>12,732,099.4</t>
+  </si>
+  <si>
+    <t>28,996,493.4</t>
+  </si>
+  <si>
+    <t>22,933,650.4</t>
+  </si>
+  <si>
+    <t>12,339,979.8</t>
+  </si>
+  <si>
+    <t>11,680,014.1</t>
+  </si>
+  <si>
+    <t>9,392,300.0</t>
+  </si>
+  <si>
+    <t>31,920,743.3</t>
+  </si>
+  <si>
+    <t>18,544,797.2</t>
+  </si>
+  <si>
+    <t>14,152,407.0</t>
+  </si>
+  <si>
+    <t>5,882,826.3</t>
+  </si>
+  <si>
+    <t>4,711,554.7</t>
+  </si>
+  <si>
+    <t>19,152,529.6</t>
+  </si>
+  <si>
+    <t>14,896,039.2</t>
+  </si>
+  <si>
+    <t>14,809,997.5</t>
+  </si>
+  <si>
+    <t>7,423,904.1</t>
+  </si>
+  <si>
+    <t>5,925,763.5</t>
+  </si>
+  <si>
+    <t>13,400,600.5</t>
+  </si>
+  <si>
+    <t>11,880,026.0</t>
+  </si>
+  <si>
+    <t>11,029,190.4</t>
+  </si>
+  <si>
+    <t>9,196,089.1</t>
+  </si>
+  <si>
+    <t>4,540,862.5</t>
   </si>
 </sst>
 </file>
@@ -1641,61 +1635,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.06498576499457699</v>
+        <v>0.057747169477945</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="G9" s="12">
+        <v>0.03761871419796144</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" s="14">
+        <v>0.05023357912059383</v>
+      </c>
+      <c r="K9" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="12">
-        <v>0.04915442632598856</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="14">
-        <v>0.03346716092112958</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>74</v>
-      </c>
       <c r="L9" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.08366777392712076</v>
+        <v>0.06406408653028965</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1539157345436697</v>
+        <v>0.1739421680154151</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S9" s="16">
-        <v>0.08637637750002235</v>
+        <v>0.1160792338430418</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>56</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="V9" s="18">
-        <v>0.0398001124889944</v>
+        <v>0.04230011031759101</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1707,61 +1701,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.03911675257291977</v>
+        <v>0.04236060119724097</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.04445662366760244</v>
+        <v>0.03223703625797703</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.0263507429561189</v>
+        <v>0.0405595724915345</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M10" s="16">
-        <v>0.03844594103058042</v>
+        <v>0.03641373317752317</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>91</v>
-      </c>
       <c r="P10" s="18">
-        <v>0.05205455906896713</v>
+        <v>0.05293020987632761</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="S10" s="16">
-        <v>0.02640748777552513</v>
+        <v>0.02134915388653697</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="V10" s="18">
-        <v>0.03239458969920291</v>
+        <v>0.03189773929498937</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1773,16 +1767,16 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03105167795146459</v>
+        <v>0.03002448872533315</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.0391164583749499</v>
+        <v>0.02381913106598831</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>76</v>
@@ -1791,43 +1785,43 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02396485499361899</v>
+        <v>0.03997523424775609</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M11" s="16">
-        <v>0.03002254203154115</v>
+        <v>0.02521547984977624</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P11" s="18">
-        <v>0.03179395038747841</v>
+        <v>0.02180961997509657</v>
       </c>
       <c r="Q11" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="R11" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="R11" s="15" t="s">
-        <v>99</v>
-      </c>
       <c r="S11" s="16">
-        <v>0.01914485514274944</v>
+        <v>0.01863268234054902</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02730627532817334</v>
+        <v>0.0278260620376122</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1839,16 +1833,16 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.0270419452653806</v>
+        <v>0.02640053099409046</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.03456277360496097</v>
+        <v>0.02072674204821615</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>78</v>
@@ -1857,43 +1851,43 @@
         <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02085354693668527</v>
+        <v>0.03895684344096045</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02397538289130974</v>
+        <v>0.02368843577757654</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02469986817345869</v>
+        <v>0.01659676340249364</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01725050452060624</v>
+        <v>0.01627344996060846</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02469067379433501</v>
+        <v>0.02681955424353598</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1905,61 +1899,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02443911712772524</v>
+        <v>0.02316742486330579</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.03426282885307316</v>
+        <v>0.01787563668286137</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="J13" s="14">
-        <v>0.01857461572330742</v>
+        <v>0.03458339059247693</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="M13" s="16">
-        <v>0.02291166243232833</v>
+        <v>0.02277131668644209</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01962535135618421</v>
+        <v>0.01463114867510263</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01311979917399392</v>
+        <v>0.01332554541214845</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02105191490170282</v>
+        <v>0.0201423320719545</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1970,7 +1964,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1979,7 +1973,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1988,7 +1982,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -1997,7 +1991,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2006,7 +2000,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2015,7 +2009,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2024,7 +2018,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2033,67 +2027,67 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2889230012534093</v>
+        <v>0.3151390813910231</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.07175586713603858</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0.0785074168135</v>
-      </c>
-      <c r="H16" s="13" t="s">
+      <c r="I16" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>124</v>
-      </c>
       <c r="J16" s="14">
-        <v>0.06515739420688285</v>
+        <v>0.05652873789471093</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1012522856430968</v>
+        <v>0.1408581513087671</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P16" s="18">
-        <v>0.07362753384123673</v>
+        <v>0.07980255424206034</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>58</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="S16" s="16">
-        <v>0.04634565877472991</v>
+        <v>0.04290803881925861</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="V16" s="18">
-        <v>0.07537571697042092</v>
+        <v>0.0468399270527478</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2102,196 +2096,196 @@
         <v>56</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D17" s="10">
-        <v>0.01761827307908401</v>
+        <v>0.02143414529006034</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G17" s="12">
-        <v>0.04410729134246662</v>
+        <v>0.02305913379798269</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J17" s="14">
-        <v>0.04543663390119198</v>
+        <v>0.04507563763948211</v>
       </c>
       <c r="K17" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="L17" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="L17" s="15" t="s">
-        <v>131</v>
-      </c>
       <c r="M17" s="16">
-        <v>0.0471948550450091</v>
+        <v>0.04542155162980612</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P17" s="18">
-        <v>0.07075177405939123</v>
+        <v>0.06899699366116221</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="S17" s="16">
-        <v>0.03392853594019672</v>
+        <v>0.03174578690602839</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V17" s="18">
-        <v>0.04528567036318549</v>
+        <v>0.04008342081709038</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D18" s="10">
-        <v>0.01064756359102</v>
+        <v>0.01692283243540409</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>120</v>
-      </c>
       <c r="G18" s="12">
-        <v>0.03491920623722484</v>
+        <v>0.01992649218541186</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J18" s="14">
-        <v>0.02752761523849761</v>
+        <v>0.03575120128467697</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>54</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02757440722830644</v>
+        <v>0.03065758899266995</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P18" s="18">
-        <v>0.06278201659679647</v>
+        <v>0.05116345292759654</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="S18" s="16">
-        <v>0.03380841743632919</v>
+        <v>0.03123066191814563</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02455664761670793</v>
+        <v>0.03010049801797006</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D19" s="10">
-        <v>0.009765989581341391</v>
+        <v>0.01048935239218316</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>121</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03386431739173568</v>
+        <v>0.01981107481148328</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J19" s="14">
-        <v>0.02233521041455812</v>
+        <v>0.03197654899628884</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>58</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01450590270613472</v>
+        <v>0.01626647540271528</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="P19" s="18">
-        <v>0.035818317333046</v>
+        <v>0.02538634404551871</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02951568000990441</v>
+        <v>0.03112009480169202</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01787923157307438</v>
+        <v>0.01880390114665623</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2300,80 +2294,80 @@
         <v>58</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D20" s="10">
-        <v>0.008866004946922976</v>
+        <v>0.007401469736015458</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>122</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03032698991010817</v>
+        <v>0.01748231869194281</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01738853748397141</v>
+        <v>0.03099279883841126</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M20" s="16">
-        <v>0.009130965864959506</v>
+        <v>0.01243996725837451</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02000372949519085</v>
+        <v>0.02035014979124954</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02849195116953676</v>
+        <v>0.02702241369617419</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="V20" s="18">
-        <v>0.0177732511939693</v>
+        <v>0.01514253284102072</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2381,7 +2375,7 @@
         <v>58</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2389,7 +2383,7 @@
         <v>56</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2397,7 +2391,7 @@
         <v>54</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2405,183 +2399,183 @@
         <v>60</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="19" t="s">
         <v>157</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2357964705321585</v>
+        <v>0.2378571700485554</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1857376946632249</v>
+        <v>0.1898090523508266</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1256612369137748</v>
+        <v>0.1257629886917333</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1048213120563506</v>
+        <v>0.1161508567808339</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D35" s="22">
-        <v>0.08860244128491605</v>
+        <v>0.08301372912842099</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D36" s="22">
-        <v>0.07003828354485842</v>
+        <v>0.0761514784417559</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04632768618636599</v>
+        <v>0.04606941069691755</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D38" s="22">
-        <v>0.04337064979074825</v>
+        <v>0.04520715321589831</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D39" s="22">
-        <v>0.03167551014890855</v>
+        <v>0.03333909904644056</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02887530616510656</v>
+        <v>0.03033011858508927</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01075995628672251</v>
+        <v>0.01152205139399076</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D42" s="22">
-        <v>0.002275570126349962</v>
+        <v>0.002378898614492933</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D43" s="22">
-        <v>0.001511964630636716</v>
+        <v>0.00140726862618264</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0009665048790851488</v>
+        <v>0.001000724378861966</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D45" s="20" t="s">
         <v>193</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2960,265 +2954,265 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1388528815580415</v>
+        <v>0.1289049474774071</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>165</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1232550253216144</v>
+        <v>0.1180332352116428</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1169718788132846</v>
+        <v>0.1250062375058343</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1635533744460556</v>
+        <v>0.131001324434429</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1641681772819235</v>
+        <v>0.1843670751817947</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="S9" s="16">
-        <v>0.09872991733819061</v>
+        <v>0.1270512204603373</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="V9" s="18">
-        <v>0.12651085779018</v>
+        <v>0.1246872111637155</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.1185346858882163</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.09747907694926698</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="J10" s="14">
+        <v>0.0920692623092359</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="M10" s="16">
+        <v>0.0673996533841132</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="O10" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="P10" s="18">
+        <v>0.1003115716034386</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="S10" s="16">
+        <v>0.08571808623697323</v>
+      </c>
+      <c r="T10" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="10">
-        <v>0.117300437603806</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.0900069635839521</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="J10" s="14">
-        <v>0.1079568346776426</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="M10" s="16">
-        <v>0.08996043940027075</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="O10" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="P10" s="18">
-        <v>0.09470797514567317</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="R10" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="S10" s="16">
-        <v>0.0982490899455437</v>
-      </c>
-      <c r="T10" s="17" t="s">
-        <v>165</v>
-      </c>
       <c r="U10" s="17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1077387170306706</v>
+        <v>0.1033855108056978</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D11" s="10">
-        <v>0.05088281429003642</v>
+        <v>0.04184432116038633</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>167</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G11" s="12">
-        <v>0.07518350005117658</v>
+        <v>0.08767339342855998</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J11" s="14">
-        <v>0.07919328687422481</v>
+        <v>0.08282357455761671</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M11" s="16">
-        <v>0.08718949486522046</v>
+        <v>0.06453560107499129</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P11" s="18">
-        <v>0.07404038982255792</v>
+        <v>0.06471794257640512</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="S11" s="16">
-        <v>0.07642160965417374</v>
+        <v>0.08006427817344902</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V11" s="18">
-        <v>0.0875960153157401</v>
+        <v>0.08317365903487597</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D12" s="10">
-        <v>0.04041961461044934</v>
+        <v>0.03541310056979217</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.05526363891222281</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0.05802720977277758</v>
+      </c>
+      <c r="K12" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0.05364790160575732</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="J12" s="14">
-        <v>0.05379001532183005</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>179</v>
-      </c>
       <c r="L12" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M12" s="16">
-        <v>0.0473900833499612</v>
+        <v>0.04957425191495818</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P12" s="18">
-        <v>0.06429657269121292</v>
+        <v>0.05048224955720734</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="S12" s="16">
-        <v>0.06698135690310511</v>
+        <v>0.07571972132180113</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03959093471786642</v>
+        <v>0.0511344069831198</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3227,64 +3221,64 @@
         <v>177</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D13" s="10">
-        <v>0.03171382592065436</v>
+        <v>0.02647124424575411</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>169</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G13" s="12">
-        <v>0.04662740761622013</v>
+        <v>0.04114403798029765</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>171</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03416889454910033</v>
+        <v>0.04463240342468514</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03876994231252145</v>
+        <v>0.0450578351641668</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P13" s="18">
-        <v>0.04391755182136987</v>
+        <v>0.02836924797654006</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="S13" s="16">
-        <v>0.05466471904714366</v>
+        <v>0.04485699582061684</v>
       </c>
       <c r="T13" s="17" t="s">
         <v>173</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="V13" s="18">
-        <v>0.03918281458629198</v>
+        <v>0.0449958037655524</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3295,7 +3289,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3304,7 +3298,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3313,7 +3307,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3322,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3331,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3340,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3349,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3358,331 +3352,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2949867944286451</v>
+        <v>0.3208850942855792</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.09970829514547232</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.1305576962285764</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.1450552368606759</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.1801641682129217</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="R16" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="S16" s="16">
+        <v>0.1219157481513492</v>
+      </c>
+      <c r="T16" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0.1436236010735626</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="J16" s="14">
-        <v>0.1443155361884531</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.104240435611078</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.1848264107248295</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="S16" s="16">
-        <v>0.1221025887802033</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>169</v>
-      </c>
       <c r="U16" s="17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1278756229835125</v>
+        <v>0.100559758144328</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.07456270467093037</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.09514523767103601</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.07953948074043235</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.1147258064953445</v>
+      </c>
+      <c r="N17" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D17" s="10">
-        <v>0.07539674304352198</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0.08883131284546245</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.1274041344338973</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0.1038507480157937</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>167</v>
-      </c>
       <c r="O17" s="17" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P17" s="18">
-        <v>0.106717079880467</v>
+        <v>0.1046688647195543</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1027030385932509</v>
+        <v>0.09482098717444745</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="V17" s="18">
-        <v>0.08481128695173652</v>
+        <v>0.08914917964372777</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.04767215057893143</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0.04016667133906952</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>179</v>
-      </c>
       <c r="F18" s="11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G18" s="12">
-        <v>0.07776922116487135</v>
+        <v>0.07233756797221068</v>
       </c>
       <c r="H18" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.06719901877468593</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.06173086752431092</v>
+      </c>
+      <c r="N18" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="J18" s="14">
-        <v>0.05225098961439231</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.06112157671405562</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>171</v>
-      </c>
       <c r="O18" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07370146964630966</v>
+        <v>0.07987773377964323</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="S18" s="16">
-        <v>0.09290944670012112</v>
+        <v>0.09427328729110077</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="V18" s="18">
-        <v>0.07949719755608127</v>
+        <v>0.08276440441245481</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.04260265773103412</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="D19" s="10">
-        <v>0.04000829375511782</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>169</v>
-      </c>
       <c r="F19" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G19" s="12">
-        <v>0.07486980709908264</v>
+        <v>0.06871324074608343</v>
       </c>
       <c r="H19" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.06566593029757223</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.05842938276845345</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="O19" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.03320331538396851</v>
+      </c>
+      <c r="Q19" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="J19" s="14">
-        <v>0.04317073661696948</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="M19" s="16">
-        <v>0.05226410910291399</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="O19" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="P19" s="18">
-        <v>0.02462779297513203</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>175</v>
-      </c>
       <c r="R19" s="15" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="S19" s="16">
-        <v>0.05089394875553221</v>
+        <v>0.04725698596781538</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="V19" s="18">
-        <v>0.07809589243537103</v>
+        <v>0.06900858627713667</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01980006325061249</v>
+        <v>0.01877405173090274</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G20" s="12">
-        <v>0.06701413852306923</v>
+        <v>0.0453560315553936</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02777708784843937</v>
+        <v>0.06249088743024774</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M20" s="16">
-        <v>0.04884563260290087</v>
+        <v>0.04698507100056885</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02350016981422509</v>
+        <v>0.0265925303034902</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="S20" s="16">
-        <v>0.04082055820783837</v>
+        <v>0.03772054687076205</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="V20" s="18">
-        <v>0.03526054481173241</v>
+        <v>0.03407519198610902</v>
       </c>
     </row>
   </sheetData>
